--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDE daily" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDE daily" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +90,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +489,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5881824.493589079</v>
+        <v>5881849.493589079</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +505,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5887634.364509613</v>
+        <v>5887659.364509613</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5881824.493589079</v>
+        <v>5881849.493589079</v>
       </c>
     </row>
     <row r="20">
@@ -617,7 +619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2883538.055988624</v>
+        <v>2883563.055988624</v>
       </c>
     </row>
     <row r="23">
@@ -652,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-05T11:08:03+00:00</t>
+          <t>2026-06-08T08:17:43+00:00</t>
         </is>
       </c>
     </row>
@@ -679,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2127,12 +2129,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2142,7 +2144,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2192,12 +2194,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2257,12 +2259,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2300,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>0</v>
@@ -2317,21 +2319,17 @@
       <c r="R24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2341,7 +2339,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -2369,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>0</v>
@@ -2386,22 +2384,26 @@
       <c r="R25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Steakhouse Prime Instant (Base, Morpho V2)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2456,17 +2458,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>Steakhouse Prime Instant (Base, Morpho V2)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2521,12 +2523,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2536,7 +2538,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2586,17 +2588,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2651,59 +2653,189 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USDC raw on Base (ALM idle)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
@@ -3149,6 +3281,1524 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2051561642.799006</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1064349366.450599</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>987212276.3484071</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0.0369675</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>98186.7631455995</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>221090.1939366975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2082334464.799006</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1064401902.960599</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1017932561.838407</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>102039.2260037818</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>225156.0092555509</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2084036164.799006</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1064419413.970599</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1019616750.828407</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>102234.0320542597</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>225352.8407620306</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2123736164.799006</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1064688073.168717</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1059048091.630289</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>106794.9594871484</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>229944.8433519359</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2182040051.964926</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1114737974.303257</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1067302077.661669</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0.0369675</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>107243.2802780138</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>236182.3146625573</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2240040051.964926</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1164805168.186478</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1075234883.778448</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>108414.0592282019</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>243144.2443427465</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2240040051.964926</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1164805168.186478</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1075234883.778448</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>108414.0592282019</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>243144.2443427465</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2240040051.964926</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1164805168.186478</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1075234883.778448</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>108414.0592282019</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>243144.2443427465</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2240040051.964926</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1165034304.849401</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1075005747.115525</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>108640.7427445041</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>243397.4315403984</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2240040051.964926</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1165106966.236165</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1074933085.728761</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>108632.3381783528</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>243397.4315403984</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2240040051.964926</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1165188936.99157</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1074851114.973356</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.037255</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>108876.0206886737</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>243650.5954089339</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2243626294.768607</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1165266619.83545</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1078359674.933157</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.037255</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>109281.8472988058</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>244065.4074049674</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2245626294.768607</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1165345509.1343</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1080280785.634308</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>108997.7064420688</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>243790.3914818484</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2245626294.768607</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1165345509.1343</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1080280785.634308</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>108997.7064420688</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>243790.3914818484</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2245626294.768607</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1165345509.1343</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1080280785.634308</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>108997.7064420688</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>243790.3914818484</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2240638278.924036</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1165551956.619256</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1075086322.30478</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>108396.8754833192</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>243213.439802333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2285638278.924036</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1215645110.019256</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1069993168.90478</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>108060.9499957423</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>248671.6677190212</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2332638836.164886</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1265706865.332211</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1066931970.832675</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.037255</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>107960.0325172923</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>254361.2719043571</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2326019522.216694</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1265795165.032042</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1060224357.184652</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>106931.0152673008</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>253342.4680662122</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2328019522.216694</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1265889084.262973</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1062130437.953721</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>107151.4870010069</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>253573.8032092804</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2330019522.216694</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1265889084.262973</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1064130437.953721</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>107382.8221440752</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>253805.1383523487</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2331019522.216694</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1265889084.262973</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1065130437.953721</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>107498.4897156094</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>253920.8059238829</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2333019522.216694</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1266154137.108079</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1066865385.108615</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>107699.166839756</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>254152.1410669512</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2334019522.216694</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1266240975.723649</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1067778546.493045</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>107804.7899995117</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>254267.8086384853</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2324020522.216694</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1266335287.025069</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1057685235.191625</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.03715916666666667</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>106637.3211925384</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>253111.2485907154</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2324020522.216694</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1266419292.307925</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1057601229.908769</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0.03706333333333333</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>106374.4173078225</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>252858.0613930635</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2374020522.216694</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1316496454.413348</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1057524067.803346</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.0369675</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>106112.2816232646</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>258388.2294385613</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2374020522.216694</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1316496454.413348</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1057524067.803346</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.0369675</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>106112.2816232646</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>258388.2294385613</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="n">
+        <v>2998286.437600456</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>6865095.288881029</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3442,7 +5092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-08T08:17:43+00:00</t>
+          <t>2026-06-09T00:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5881849.493589079</v>
+        <v>5881849.48368835</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5887659.364509613</v>
+        <v>5887659.354608884</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5881849.493589079</v>
+        <v>5881849.48368835</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2883563.055988624</v>
+        <v>2883563.046087895</v>
       </c>
     </row>
     <row r="23">
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T00:21:19+00:00</t>
+          <t>2026-06-09T16:55:08+00:00</t>
         </is>
       </c>
     </row>
@@ -920,13 +920,13 @@
         <v>0.285693030071776</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>368618.5654926595</v>
+        <v>368618.5654925361</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1360446.05075858</v>
+        <v>1360446.050758457</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>28071.10925958815</v>
+        <v>28071.10925971164</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>325000000</v>
@@ -989,13 +989,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>742958.8343878307</v>
+        <v>742958.8343875818</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>742958.8343878307</v>
+        <v>742958.8343875818</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>2409838.915117185</v>
+        <v>2409838.915117434</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1054,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>727558.571391411</v>
+        <v>727558.5713911672</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>727558.571391411</v>
+        <v>727558.5713911672</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>55405.17505672096</v>
+        <v>55405.17505696471</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1188,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>393559.0910003756</v>
+        <v>393559.0910002437</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>393559.0910003756</v>
+        <v>393559.0910002437</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>518064.4904481069</v>
+        <v>518064.4904482387</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1253,13 +1253,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>285831.5987637122</v>
+        <v>285831.5987636165</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>285831.5987637122</v>
+        <v>285831.5987636165</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-97553.39876371222</v>
+        <v>-97553.39876361647</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1318,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>144944.19925336</v>
+        <v>144944.1992533115</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>144944.19925336</v>
+        <v>144944.1992533115</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-140943.0608594039</v>
+        <v>-140943.0608593553</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>142040.2802810775</v>
+        <v>142040.2802810299</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>142040.2802810775</v>
+        <v>142040.2802810299</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>260899.5297189225</v>
+        <v>260899.5297189701</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>71020.14014053873</v>
+        <v>71020.14014051494</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>71020.14014053873</v>
+        <v>71020.14014051494</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-71020.14014053873</v>
+        <v>-71020.14014051494</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>71020.14014053873</v>
+        <v>71020.14014051494</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>71020.14014053873</v>
+        <v>71020.14014051494</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-62981.17264953873</v>
+        <v>-62981.17264951494</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>20151.75270383987</v>
+        <v>20151.75270383312</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>20151.75270383987</v>
+        <v>20151.75270383312</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-1556.143936839869</v>
+        <v>-1556.143936833118</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1637,31 +1637,31 @@
         <v>15806005.09627441</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>5696.258105779171</v>
+        <v>5696.25251297</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>5696.258105779171</v>
+        <v>5696.25251297</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>5610706.08878279</v>
+        <v>5610706.088982533</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>15938.92530850911</v>
+        <v>15938.9253090712</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>15938.92530850911</v>
+        <v>15938.9253090712</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-10242.66720272994</v>
+        <v>-10242.6727961012</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>5078.023090445714</v>
+        <v>5078.023090444013</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>5078.023090445714</v>
+        <v>5078.023090444013</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-6767.559097445715</v>
+        <v>-6767.559097444013</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>2868.626348277146</v>
+        <v>2868.626348276186</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>2868.626348277146</v>
+        <v>2868.626348276186</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-336.2076617992811</v>
+        <v>-336.2076617983201</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>2844.666327578539</v>
+        <v>2844.666327577586</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>2844.666327578539</v>
+        <v>2844.666327577586</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>50.5530540991971</v>
+        <v>50.55305410015013</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1897,31 +1897,31 @@
         <v>1002368.85473053</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2335.900436310044</v>
+        <v>2335.89612839</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>2335.900436310044</v>
+        <v>2335.89612839</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>964317.491640855</v>
+        <v>964317.4917947092</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>2739.438535852252</v>
+        <v>2739.438536288405</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2739.438535852252</v>
+        <v>2739.438536288405</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-403.5380995422083</v>
+        <v>-403.5424078984047</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>1096.700894183939</v>
+        <v>1096.700894183572</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1096.700894183939</v>
+        <v>1096.700894183572</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-1096.700894183139</v>
+        <v>-1096.700894182772</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>10.47959421369825</v>
+        <v>10.47959421369474</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>10.47959421369825</v>
+        <v>10.47959421369474</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>6369.547711786302</v>
+        <v>6369.547711786306</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2110,13 +2110,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>6.403946051331602</v>
+        <v>6.403946051329457</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>6.403946051331602</v>
+        <v>6.403946051329457</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-2260.675072051331</v>
+        <v>-2260.67507205133</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:08+00:00</t>
+          <t>2026-06-09T22:25:20+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:20+00:00</t>
+          <t>2026-06-10T10:52:05+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:05+00:00</t>
+          <t>2026-06-10T15:01:21+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -77,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,12 +86,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,13 +502,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5809.870920534274</v>
+        <v>5809.871176809525</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5887659.354608884</v>
+        <v>5887659.35486516</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +530,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2998286.437600456</v>
+        <v>2998286.45222342</v>
       </c>
     </row>
     <row r="10">
@@ -543,7 +546,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>6137201.885615556</v>
+        <v>6137201.90023852</v>
       </c>
     </row>
     <row r="13">
@@ -565,7 +568,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2998286.437600456</v>
+        <v>2998286.45222342</v>
       </c>
     </row>
     <row r="15">
@@ -575,13 +578,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-3866808.851280573</v>
+        <v>-3866809.017764181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>6865095.288881029</v>
+        <v>6865095.469987601</v>
       </c>
     </row>
     <row r="18">
@@ -613,13 +616,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-2998286.437600456</v>
+        <v>-2998286.45222342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2883563.046087895</v>
+        <v>2883563.03146493</v>
       </c>
     </row>
     <row r="23">
@@ -654,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T15:01:21+00:00</t>
+          <t>2026-06-23T21:34:37+00:00</t>
         </is>
       </c>
     </row>
@@ -920,13 +923,13 @@
         <v>0.285693030071776</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>368618.5654925361</v>
+        <v>368618.5672903283</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1360446.050758457</v>
+        <v>1360446.052556249</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>28071.10925971164</v>
+        <v>28071.10746191938</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>325000000</v>
@@ -989,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>742958.8343875818</v>
+        <v>742958.8380110717</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>742958.8343875818</v>
+        <v>742958.8380110717</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>2409838.915117434</v>
+        <v>2409838.911493944</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1054,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>727558.5713911672</v>
+        <v>727558.5749395484</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>727558.5713911672</v>
+        <v>727558.5749395484</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>55405.17505696471</v>
+        <v>55405.17150858356</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1188,13 +1191,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>393559.0910002437</v>
+        <v>393559.0929196736</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>393559.0910002437</v>
+        <v>393559.0929196736</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>518064.4904482387</v>
+        <v>518064.4885288089</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1253,13 +1256,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>285831.5987636165</v>
+        <v>285831.6001576478</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>285831.5987636165</v>
+        <v>285831.6001576478</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-97553.39876361647</v>
+        <v>-97553.40015764782</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1318,13 +1321,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>144944.1992533115</v>
+        <v>144944.1999602199</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>144944.1992533115</v>
+        <v>144944.1999602199</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-140943.0608593553</v>
+        <v>-140943.0615662638</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1383,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>142040.2802810299</v>
+        <v>142040.2809737755</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>142040.2802810299</v>
+        <v>142040.2809737755</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>260899.5297189701</v>
+        <v>260899.5290262245</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1452,13 +1455,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>71020.14014051494</v>
+        <v>71020.14048688777</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>71020.14014051494</v>
+        <v>71020.14048688777</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-71020.14014051494</v>
+        <v>-71020.14048688777</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>71020.14014051494</v>
+        <v>71020.14048688777</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>71020.14014051494</v>
+        <v>71020.14048688777</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-62981.17264951494</v>
+        <v>-62981.17299588778</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>20151.75270383312</v>
+        <v>20151.75280211538</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>20151.75270383312</v>
+        <v>20151.75280211538</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-1556.143936833118</v>
+        <v>-1556.144035115376</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1658,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>15938.9253090712</v>
+        <v>15938.92538680705</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>15938.9253090712</v>
+        <v>15938.92538680705</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-10242.6727961012</v>
+        <v>-10242.67287383705</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1720,13 +1723,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>5078.023090444013</v>
+        <v>5078.023115210076</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>5078.023090444013</v>
+        <v>5078.023115210076</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-6767.559097444013</v>
+        <v>-6767.559122210076</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1785,13 +1788,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>2868.626348276186</v>
+        <v>2868.626362266783</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>2868.626348276186</v>
+        <v>2868.626362266783</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-336.2076617983201</v>
+        <v>-336.2076757889183</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1853,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>2844.666327577586</v>
+        <v>2844.666341451329</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>2844.666327577586</v>
+        <v>2844.666341451329</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>50.55305410015013</v>
+        <v>50.5530402264075</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1915,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>2739.438536288405</v>
+        <v>2739.43854964894</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2739.438536288405</v>
+        <v>2739.43854964894</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-403.5424078984047</v>
+        <v>-403.5424212589401</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1983,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>1096.700894183572</v>
+        <v>1096.700899532299</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1096.700894183572</v>
+        <v>1096.700899532299</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-1096.700894182772</v>
+        <v>-1096.7008995315</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2045,13 +2048,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>10.47959421369474</v>
+        <v>10.47959426480484</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>10.47959421369474</v>
+        <v>10.47959426480484</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>6369.547711786306</v>
+        <v>6369.547711735195</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2110,13 +2113,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>6.403946051329457</v>
+        <v>6.403946082562188</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>6.403946051329457</v>
+        <v>6.403946082562188</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-2260.67507205133</v>
+        <v>-2260.675072082562</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2852,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2867,185 +2870,367 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2998286.437600456</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3138915.4480151</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1062479073.381894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>6137201.885615556</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>999543295.5838717</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>62935777.79802263</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.04312000189646037</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (tbill_3m), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.03685357142857143</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>6865095.288881029</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0.0371146726980668</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>2998286.437600456</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.03747046067346277</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-3866808.851280573</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-56.495412229976</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>442756.1742453264</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3441042.626468746</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2998286.45222342</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>442756.1742453264</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ramp_months</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>24</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ref_rate_kind</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tbill_3m</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>999543295.5838717</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2794456.843190622</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>62935777.79802263</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>203829.6090327982</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2998286.45222342</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3138915.4480151</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>6137201.90023852</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>6865095.469987601</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2998286.45222342</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-3866809.017764181</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ramp_months</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ref_rate_kind</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tbill_3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>1 (SoM) → 1 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -3309,7 +3494,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -3419,10 +3604,10 @@
         <v>987212276.3484071</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -3431,13 +3616,13 @@
         <v>0.0367</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0369675</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>98186.7631455995</v>
+        <v>98186.76335165235</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>221090.1939366975</v>
+        <v>221090.1993838481</v>
       </c>
     </row>
     <row r="7">
@@ -3468,10 +3653,10 @@
         <v>1017932561.838407</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -3480,13 +3665,13 @@
         <v>0.0369</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>102039.2260037818</v>
+        <v>102039.2263020581</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>225156.0092555509</v>
+        <v>225156.0148562206</v>
       </c>
     </row>
     <row r="8">
@@ -3517,10 +3702,10 @@
         <v>1019616750.828407</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -3529,13 +3714,13 @@
         <v>0.0369</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>102234.0320542597</v>
+        <v>102234.0323609259</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>225352.8407620306</v>
+        <v>225352.8463711774</v>
       </c>
     </row>
     <row r="9">
@@ -3566,10 +3751,10 @@
         <v>1059048091.630289</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -3578,13 +3763,13 @@
         <v>0.0369</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106794.9594871484</v>
+        <v>106794.9599902446</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>229944.8433519359</v>
+        <v>229944.849158851</v>
       </c>
     </row>
     <row r="10">
@@ -3615,10 +3800,10 @@
         <v>1067302077.661669</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -3627,13 +3812,13 @@
         <v>0.0367</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0369675</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>107243.2802780138</v>
+        <v>107243.2808220058</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>236182.3146625573</v>
+        <v>236182.3207596953</v>
       </c>
     </row>
     <row r="11">
@@ -3664,10 +3849,10 @@
         <v>1075234883.778448</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -3676,13 +3861,13 @@
         <v>0.0368</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>108414.0592282019</v>
+        <v>108414.0598117117</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>243144.2443427465</v>
+        <v>243144.2507288156</v>
       </c>
     </row>
     <row r="12">
@@ -3713,10 +3898,10 @@
         <v>1075234883.778448</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -3725,13 +3910,13 @@
         <v>0.0368</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>108414.0592282019</v>
+        <v>108414.0598117117</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>243144.2443427465</v>
+        <v>243144.2507288156</v>
       </c>
     </row>
     <row r="13">
@@ -3762,10 +3947,10 @@
         <v>1075234883.778448</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -3774,13 +3959,13 @@
         <v>0.0368</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>108414.0592282019</v>
+        <v>108414.0598117117</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>243144.2443427465</v>
+        <v>243144.2507288156</v>
       </c>
     </row>
     <row r="14">
@@ -3811,10 +3996,10 @@
         <v>1075005747.115525</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -3823,13 +4008,13 @@
         <v>0.0369</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>108640.7427445041</v>
+        <v>108640.7433270945</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>243397.4315403984</v>
+        <v>243397.4379266896</v>
       </c>
     </row>
     <row r="15">
@@ -3860,10 +4045,10 @@
         <v>1074933085.728761</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -3872,13 +4057,13 @@
         <v>0.0369</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>108632.3381783528</v>
+        <v>108632.3387605813</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>243397.4315403984</v>
+        <v>243397.4379266896</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +4094,10 @@
         <v>1074851114.973356</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -3921,13 +4106,13 @@
         <v>0.037</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.037255</v>
+        <v>0.03725500007901918</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>108876.0206886737</v>
+        <v>108876.0212702717</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>243650.5954089339</v>
+        <v>243650.601795003</v>
       </c>
     </row>
     <row r="17">
@@ -3958,10 +4143,10 @@
         <v>1078359674.933157</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -3970,13 +4155,13 @@
         <v>0.037</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.037255</v>
+        <v>0.03725500007901918</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>109281.8472988058</v>
+        <v>109281.847897882</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>244065.4074049674</v>
+        <v>244065.4138089017</v>
       </c>
     </row>
     <row r="18">
@@ -4007,10 +4192,10 @@
         <v>1080280785.634308</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -4019,13 +4204,13 @@
         <v>0.0368</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>108997.7064420688</v>
+        <v>108997.7070507151</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>243790.3914818484</v>
+        <v>243790.3978957458</v>
       </c>
     </row>
     <row r="19">
@@ -4056,10 +4241,10 @@
         <v>1080280785.634308</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -4068,13 +4253,13 @@
         <v>0.0368</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>108997.7064420688</v>
+        <v>108997.7070507151</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>243790.3914818484</v>
+        <v>243790.3978957458</v>
       </c>
     </row>
     <row r="20">
@@ -4105,10 +4290,10 @@
         <v>1080280785.634308</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -4117,13 +4302,13 @@
         <v>0.0368</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>108997.7064420688</v>
+        <v>108997.7070507151</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>243790.3914818484</v>
+        <v>243790.3978957458</v>
       </c>
     </row>
     <row r="21">
@@ -4154,10 +4339,10 @@
         <v>1075086322.30478</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -4166,13 +4351,13 @@
         <v>0.0368</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>108396.8754833192</v>
+        <v>108396.876066089</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>243213.439802333</v>
+        <v>243213.4461913823</v>
       </c>
     </row>
     <row r="22">
@@ -4203,10 +4388,10 @@
         <v>1069993168.90478</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -4215,13 +4400,13 @@
         <v>0.0369</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>108060.9499957423</v>
+        <v>108060.9505533622</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>248671.6677190212</v>
+        <v>248671.6743324632</v>
       </c>
     </row>
     <row r="23">
@@ -4252,10 +4437,10 @@
         <v>1066931970.832675</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -4264,13 +4449,13 @@
         <v>0.037</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.037255</v>
+        <v>0.03725500007901918</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>107960.0325172923</v>
+        <v>107960.0330594406</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>254361.2719043571</v>
+        <v>254361.2787517136</v>
       </c>
     </row>
     <row r="24">
@@ -4301,10 +4486,10 @@
         <v>1060224357.184652</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -4313,13 +4498,13 @@
         <v>0.0369</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>106931.0152673008</v>
+        <v>106931.0157762567</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>253342.4680662122</v>
+        <v>253342.4748808162</v>
       </c>
     </row>
     <row r="25">
@@ -4350,10 +4535,10 @@
         <v>1062130437.953721</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -4362,13 +4547,13 @@
         <v>0.0369</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>107151.4870010069</v>
+        <v>107151.4875194581</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>253573.8032092804</v>
+        <v>253573.8100338476</v>
       </c>
     </row>
     <row r="26">
@@ -4399,10 +4584,10 @@
         <v>1064130437.953721</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -4411,13 +4596,13 @@
         <v>0.0369</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>107382.8221440752</v>
+        <v>107382.8226724895</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>253805.1383523487</v>
+        <v>253805.145186879</v>
       </c>
     </row>
     <row r="27">
@@ -4448,10 +4633,10 @@
         <v>1065130437.953721</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -4460,13 +4645,13 @@
         <v>0.0369</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>107498.4897156094</v>
+        <v>107498.4902490052</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>253920.8059238829</v>
+        <v>253920.8127633947</v>
       </c>
     </row>
     <row r="28">
@@ -4497,10 +4682,10 @@
         <v>1066865385.108615</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -4509,13 +4694,13 @@
         <v>0.0369</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>107699.166839756</v>
+        <v>107699.1673817946</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>254152.1410669512</v>
+        <v>254152.1479164262</v>
       </c>
     </row>
     <row r="29">
@@ -4546,10 +4731,10 @@
         <v>1067778546.493045</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -4558,13 +4743,13 @@
         <v>0.0369</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>107804.7899995117</v>
+        <v>107804.7905460993</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>254267.8086384853</v>
+        <v>254267.8154929419</v>
       </c>
     </row>
     <row r="30">
@@ -4595,10 +4780,10 @@
         <v>1057685235.191625</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -4607,13 +4792,13 @@
         <v>0.0369</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03715916666666667</v>
+        <v>0.03715916674568585</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>106637.3211925384</v>
+        <v>106637.3216888455</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>253111.2485907154</v>
+        <v>253111.2553953613</v>
       </c>
     </row>
     <row r="31">
@@ -4644,10 +4829,10 @@
         <v>1057601229.908769</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -4656,13 +4841,13 @@
         <v>0.0368</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.03706333333333333</v>
+        <v>0.03706333341235252</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>106374.4173078225</v>
+        <v>106374.4178034891</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>252858.0613930635</v>
+        <v>252858.0681974873</v>
       </c>
     </row>
     <row r="32">
@@ -4693,10 +4878,10 @@
         <v>1057524067.803346</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -4705,13 +4890,13 @@
         <v>0.0367</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0369675</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>106112.2816232646</v>
+        <v>106112.2821185468</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>258388.2294385613</v>
+        <v>258388.2364920636</v>
       </c>
     </row>
     <row r="33">
@@ -4742,10 +4927,10 @@
         <v>1057524067.803346</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -4754,17 +4939,17 @@
         <v>0.0367</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.0369675</v>
+        <v>0.03696750007901918</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>106112.2816232646</v>
+        <v>106112.2821185468</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>258388.2294385613</v>
+        <v>258388.2364920636</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>
@@ -4782,10 +4967,10 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" s="10" t="n">
-        <v>2998286.437600456</v>
+        <v>2998286.45222342</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>6865095.288881029</v>
+        <v>6865095.469987601</v>
       </c>
     </row>
   </sheetData>
@@ -5123,7 +5308,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>E8 — Janus Henderson Anemoy AAA CLO (JAAA)</t>
         </is>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T21:34:37+00:00</t>
+          <t>2026-06-23T22:21:57+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T22:21:57+00:00</t>
+          <t>2026-07-03T06:32:32+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03T06:32:32+00:00</t>
+          <t>2026-07-07T14:51:37+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5881849.48368835</v>
+        <v>5877723.727508349</v>
       </c>
     </row>
     <row r="5">
@@ -508,7 +508,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5887659.35486516</v>
+        <v>5883533.598685158</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5881849.48368835</v>
+        <v>5877723.727508349</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +622,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2883563.03146493</v>
+        <v>2879437.275284929</v>
       </c>
     </row>
     <row r="23">
@@ -657,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:37+00:00</t>
+          <t>2026-07-10T11:17:32+00:00</t>
         </is>
       </c>
     </row>
@@ -923,13 +923,13 @@
         <v>0.285693030071776</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>368618.5672903283</v>
+        <v>368752.0064117025</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1360446.052556249</v>
+        <v>1360579.491677623</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>28071.10746191938</v>
+        <v>27937.66834054511</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>325000000</v>
@@ -992,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>742958.8380110717</v>
+        <v>743227.7874980445</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>742958.8380110717</v>
+        <v>743227.7874980445</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>2409838.911493944</v>
+        <v>2409569.962006971</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1057,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>727558.5749395484</v>
+        <v>727821.9495647115</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>727558.5749395484</v>
+        <v>727821.9495647115</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>55405.17150858356</v>
+        <v>55141.79688342047</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1191,13 +1191,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>393559.0929196736</v>
+        <v>393701.5604571992</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>393559.0929196736</v>
+        <v>393701.5604571992</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>518064.4885288089</v>
+        <v>517922.0209912833</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1256,13 +1256,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>285831.6001576478</v>
+        <v>285935.0705765863</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>285831.6001576478</v>
+        <v>285935.0705765863</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-97553.40015764782</v>
+        <v>-97656.87057658631</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1321,13 +1321,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>144944.1999602199</v>
+        <v>144996.6694460441</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>144944.1999602199</v>
+        <v>144996.6694460441</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-140943.0615662638</v>
+        <v>-140995.531052088</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1386,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>142040.2809737755</v>
+        <v>142091.6992472289</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>142040.2809737755</v>
+        <v>142091.6992472289</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>260899.5290262245</v>
+        <v>260848.1107527711</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1455,13 +1455,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>71020.14048688777</v>
+        <v>71045.84962361443</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>71020.14048688777</v>
+        <v>71045.84962361443</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-71020.14048688777</v>
+        <v>-71045.84962361443</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>71020.14048688777</v>
+        <v>71045.84962361443</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>71020.14048688777</v>
+        <v>71045.84962361443</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-62981.17299588778</v>
+        <v>-63006.88213261442</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1593,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>20151.75280211538</v>
+        <v>20159.04769289593</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>20151.75280211538</v>
+        <v>20159.04769289593</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-1556.144035115376</v>
+        <v>-1563.438925895926</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>15938.92538680705</v>
+        <v>15944.69524320603</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>15938.92538680705</v>
+        <v>15944.69524320603</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-10242.67287383705</v>
+        <v>-10248.44273023603</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>5078.023115210076</v>
+        <v>5079.861348557335</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>5078.023115210076</v>
+        <v>5079.861348557335</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-6767.559122210076</v>
+        <v>-6769.397355557335</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1788,13 +1788,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>2868.626362266783</v>
+        <v>2869.664798784363</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>2868.626362266783</v>
+        <v>2869.664798784363</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-336.2076757889183</v>
+        <v>-337.2461123064974</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1853,13 +1853,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>2844.666341451329</v>
+        <v>2845.696104493371</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>2844.666341451329</v>
+        <v>2845.696104493371</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>50.5530402264075</v>
+        <v>49.52327718436504</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1918,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>2739.43854964894</v>
+        <v>2740.430220458718</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2739.43854964894</v>
+        <v>2740.430220458718</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-403.5424212589401</v>
+        <v>-404.534092068718</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1937,12 +1937,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1956,40 +1956,40 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>3688.95154</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>10068.978846</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>6380.027306</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>8e-10</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>8e-10</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>386052.7774282494</v>
+        <v>10068.978846</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>1096.700899532299</v>
+        <v>28.61436627825083</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1096.700899532299</v>
+        <v>28.61436627825083</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-1096.7008995315</v>
+        <v>-28.61436627825083</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2002,12 +2002,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2017,44 +2017,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3688.95154</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>6380.027306</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>6380.027306</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>6380.027306</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3688.95154</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>10.47959426480484</v>
+        <v>0</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>10.47959426480484</v>
+        <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>6369.547711735195</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2067,12 +2067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2086,40 +2086,40 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2254.271126</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-2254.271126</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-2254.271126</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-2254.271126</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>2254.271126</v>
+        <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>6.403946082562188</v>
+        <v>0</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>6.403946082562188</v>
+        <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-2260.675072082562</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2132,12 +2132,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2197,12 +2197,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>2254.271126</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>-2254.271126</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDE daily" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SDE daily" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-10T11:17:32+00:00</t>
+          <t>2026-07-31T00:09:15+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-02/grove_settlement_february_2026.xlsx
+++ b/reports/grove/2026-02/grove_settlement_february_2026.xlsx
@@ -2921,7 +2921,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
